--- a/data/gravel/Open WI.DE 2025.xlsx
+++ b/data/gravel/Open WI.DE 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBFE503-0AFD-D649-A0E7-61E10931CBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63E4066-C7AE-434C-A89C-A21C0F4A2846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6160" yWindow="3200" windowWidth="22640" windowHeight="13300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -332,6 +332,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -678,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1364,159 +1382,189 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>71</v>
-      </c>
-      <c r="B54">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>74</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B60">
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="B62">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>81</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B70">
-        <v>2800</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>90</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>102</v>
       </c>
     </row>
